--- a/artfynd/A 13458-2024 artfynd.xlsx
+++ b/artfynd/A 13458-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122587032</v>
       </c>
       <c r="B2" t="n">
-        <v>57380</v>
+        <v>57381</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>122587064</v>
       </c>
       <c r="B3" t="n">
-        <v>57299</v>
+        <v>57300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 13458-2024 artfynd.xlsx
+++ b/artfynd/A 13458-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122587032</v>
+        <v>122587064</v>
       </c>
       <c r="B2" t="n">
-        <v>57475</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102119</v>
+        <v>100067</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +708,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>3K-</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518187</v>
+        <v>518215</v>
       </c>
       <c r="R2" t="n">
-        <v>6585721</v>
+        <v>6585885</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -754,22 +754,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-06-03</t>
+          <t>2020-03-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-06-03</t>
+          <t>2020-03-19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Sågs kort i motljus när passerade.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122587064</v>
+        <v>122587032</v>
       </c>
       <c r="B3" t="n">
-        <v>57394</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57942</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100067</v>
+        <v>102119</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -834,14 +834,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>3K-</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -850,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518215</v>
+        <v>518187</v>
       </c>
       <c r="R3" t="n">
-        <v>6585885</v>
+        <v>6585721</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -880,27 +875,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-03-19</t>
+          <t>2020-06-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-03-19</t>
+          <t>2020-06-03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Sågs kort i motljus när passerade.</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 13458-2024 artfynd.xlsx
+++ b/artfynd/A 13458-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122587064</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,8 +924,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122587032</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>